--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7322,0.0852,0.0501,0.1312</t>
-  </si>
-  <si>
-    <t>0.2656,0.0055,0.0013,0.9055</t>
-  </si>
-  <si>
-    <t>0.6081,0.0217,0.0225,0.4400</t>
-  </si>
-  <si>
-    <t>0.3317,0.0304,0.0076,0.7860</t>
-  </si>
-  <si>
-    <t>0.9955,0.0016,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9895,0.0051,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9921,0.0055,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9798,0.0152,0.0039,0.0012</t>
-  </si>
-  <si>
-    <t>0.9931,0.0054,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0064,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9867,0.0106,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.4025,0.1479,0.4579,0.0043</t>
-  </si>
-  <si>
-    <t>0.5499,0.0542,0.5292,0.0051</t>
-  </si>
-  <si>
-    <t>0.5196,0.0301,0.6420,0.0021</t>
-  </si>
-  <si>
-    <t>0.1209,0.0237,0.8913,0.0011</t>
-  </si>
-  <si>
-    <t>0.7692,0.0096,0.3050,0.0045</t>
-  </si>
-  <si>
-    <t>0.0042,0.9889,0.0156,0.0005</t>
-  </si>
-  <si>
-    <t>0.0182,0.9735,0.0138,0.0010</t>
-  </si>
-  <si>
-    <t>0.0610,0.9295,0.0157,0.0012</t>
-  </si>
-  <si>
-    <t>0.0163,0.9737,0.0110,0.0011</t>
-  </si>
-  <si>
-    <t>0.0030,0.9911,0.0146,0.0004</t>
-  </si>
-  <si>
-    <t>0.6241,0.0201,0.4285,0.0096</t>
-  </si>
-  <si>
-    <t>0.3332,0.0420,0.6972,0.0104</t>
-  </si>
-  <si>
-    <t>0.0794,0.0106,0.9402,0.0023</t>
-  </si>
-  <si>
-    <t>0.2797,0.0041,0.8814,0.0004</t>
-  </si>
-  <si>
-    <t>0.0743,0.0060,0.9557,0.0005</t>
-  </si>
-  <si>
-    <t>0.1515,0.0184,0.8587,0.0171</t>
-  </si>
-  <si>
-    <t>0.0172,0.0054,0.9696,0.0127</t>
-  </si>
-  <si>
-    <t>0.5038,0.5687,0.0187,0.0064</t>
-  </si>
-  <si>
-    <t>0.4081,0.0967,0.6042,0.0097</t>
-  </si>
-  <si>
-    <t>0.0039,0.1445,0.9794,0.0011</t>
-  </si>
-  <si>
-    <t>0.1492,0.4349,0.4927,0.0062</t>
-  </si>
-  <si>
-    <t>0.8382,0.0631,0.0528,0.0525</t>
-  </si>
-  <si>
-    <t>0.8183,0.1291,0.0846,0.0076</t>
-  </si>
-  <si>
-    <t>0.8380,0.2103,0.0210,0.0020</t>
-  </si>
-  <si>
-    <t>0.0096,0.9542,0.2691,0.0004</t>
-  </si>
-  <si>
-    <t>0.0814,0.7406,0.2571,0.0143</t>
-  </si>
-  <si>
-    <t>0.1761,0.0241,0.8634,0.0075</t>
-  </si>
-  <si>
-    <t>0.0596,0.0525,0.9161,0.0081</t>
-  </si>
-  <si>
-    <t>0.3078,0.0296,0.5179,0.1625</t>
-  </si>
-  <si>
-    <t>0.0375,0.0252,0.9522,0.0053</t>
-  </si>
-  <si>
-    <t>0.0025,0.9863,0.0544,0.0002</t>
-  </si>
-  <si>
-    <t>0.0171,0.2024,0.9293,0.0008</t>
-  </si>
-  <si>
-    <t>0.0565,0.4239,0.0188,0.8543</t>
-  </si>
-  <si>
-    <t>0.0092,0.9681,0.0752,0.0060</t>
-  </si>
-  <si>
-    <t>0.0210,0.9565,0.0506,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.9908,0.1684,0.0008</t>
-  </si>
-  <si>
-    <t>0.0614,0.3308,0.8313,0.0209</t>
-  </si>
-  <si>
-    <t>0.0140,0.2169,0.9474,0.0009</t>
-  </si>
-  <si>
-    <t>0.0263,0.0064,0.9761,0.0009</t>
-  </si>
-  <si>
-    <t>0.0515,0.0099,0.9585,0.0041</t>
-  </si>
-  <si>
-    <t>0.0057,0.0452,0.9800,0.0033</t>
-  </si>
-  <si>
-    <t>0.0227,0.0028,0.9841,0.0008</t>
-  </si>
-  <si>
-    <t>0.9671,0.0408,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.9660,0.0319,0.0068,0.0013</t>
-  </si>
-  <si>
-    <t>0.9751,0.0229,0.0034,0.0014</t>
-  </si>
-  <si>
-    <t>0.0027,0.0715,0.9861,0.0005</t>
-  </si>
-  <si>
-    <t>0.9841,0.0132,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.9960,0.0021,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9587,0.0324,0.0112,0.0030</t>
-  </si>
-  <si>
-    <t>0.0424,0.5161,0.7958,0.0057</t>
-  </si>
-  <si>
-    <t>0.0729,0.2259,0.8057,0.0050</t>
-  </si>
-  <si>
-    <t>0.0120,0.0812,0.9621,0.0064</t>
-  </si>
-  <si>
-    <t>0.0013,0.9382,0.8218,0.0003</t>
-  </si>
-  <si>
-    <t>0.0045,0.0309,0.9832,0.0045</t>
-  </si>
-  <si>
-    <t>0.0134,0.9623,0.0632,0.0016</t>
-  </si>
-  <si>
-    <t>0.0066,0.9828,0.0177,0.0004</t>
-  </si>
-  <si>
-    <t>0.5110,0.1579,0.3983,0.0144</t>
-  </si>
-  <si>
-    <t>0.5405,0.4934,0.0487,0.0032</t>
-  </si>
-  <si>
-    <t>0.0100,0.0993,0.9600,0.0043</t>
-  </si>
-  <si>
-    <t>0.0034,0.8827,0.7294,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.6742,0.8610,0.0006</t>
-  </si>
-  <si>
-    <t>0.0043,0.9694,0.1181,0.0018</t>
-  </si>
-  <si>
-    <t>0.0107,0.9032,0.4771,0.0044</t>
-  </si>
-  <si>
-    <t>0.1491,0.0021,0.0490,0.8197</t>
-  </si>
-  <si>
-    <t>0.0095,0.0015,0.0006,0.9969</t>
-  </si>
-  <si>
-    <t>0.0158,0.0291,0.0049,0.9867</t>
-  </si>
-  <si>
-    <t>0.0352,0.0174,0.0061,0.9796</t>
-  </si>
-  <si>
-    <t>0.0214,0.0273,0.0061,0.9833</t>
-  </si>
-  <si>
-    <t>0.0095,0.0089,0.0023,0.9933</t>
-  </si>
-  <si>
-    <t>0.0086,0.8576,0.6949,0.0010</t>
-  </si>
-  <si>
-    <t>0.0013,0.8721,0.8691,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.7206,0.8779,0.0004</t>
-  </si>
-  <si>
-    <t>0.0268,0.1163,0.9349,0.0018</t>
-  </si>
-  <si>
-    <t>0.0004,0.8551,0.9398,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.9064,0.6612,0.0011</t>
-  </si>
-  <si>
-    <t>0.9883,0.0087,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9782,0.0183,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.9951,0.0037,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9920,0.0055,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9907,0.0054,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9928,0.0045,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9829,0.0144,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.9855,0.0111,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0014,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9972,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0006,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9930,0.0033,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0022,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9874,0.0094,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.0235,0.0157,0.9623,0.0103</t>
-  </si>
-  <si>
-    <t>0.0628,0.0087,0.9630,0.0009</t>
-  </si>
-  <si>
-    <t>0.6059,0.0934,0.3317,0.0176</t>
-  </si>
-  <si>
-    <t>0.4548,0.0305,0.6142,0.0099</t>
-  </si>
-  <si>
-    <t>0.0114,0.9748,0.0164,0.0010</t>
-  </si>
-  <si>
-    <t>0.0114,0.9822,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.1626,0.8727,0.0104,0.0012</t>
-  </si>
-  <si>
-    <t>0.1617,0.8577,0.0181,0.0016</t>
-  </si>
-  <si>
-    <t>0.0417,0.9420,0.0059,0.0078</t>
-  </si>
-  <si>
-    <t>0.0134,0.9775,0.0075,0.0006</t>
-  </si>
-  <si>
-    <t>0.2393,0.7297,0.0408,0.0019</t>
-  </si>
-  <si>
-    <t>0.3572,0.5391,0.1509,0.0337</t>
-  </si>
-  <si>
-    <t>0.2464,0.0075,0.8626,0.0026</t>
-  </si>
-  <si>
-    <t>0.3832,0.3832,0.1614,0.0059</t>
-  </si>
-  <si>
-    <t>0.4349,0.0955,0.5429,0.0045</t>
-  </si>
-  <si>
-    <t>0.3534,0.3960,0.1233,0.3235</t>
-  </si>
-  <si>
-    <t>0.0072,0.9736,0.1565,0.0015</t>
-  </si>
-  <si>
-    <t>0.0046,0.9798,0.0656,0.0021</t>
-  </si>
-  <si>
-    <t>0.0275,0.9390,0.0232,0.0250</t>
-  </si>
-  <si>
-    <t>0.0006,0.9775,0.7472,0.0003</t>
-  </si>
-  <si>
-    <t>0.0115,0.9734,0.0482,0.0004</t>
-  </si>
-  <si>
-    <t>0.5528,0.4473,0.0536,0.0024</t>
-  </si>
-  <si>
-    <t>0.5052,0.4482,0.0690,0.0027</t>
-  </si>
-  <si>
-    <t>0.9858,0.0048,0.0026,0.0014</t>
-  </si>
-  <si>
-    <t>0.9891,0.0015,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.9717,0.0160,0.0041,0.0040</t>
-  </si>
-  <si>
-    <t>0.9807,0.0104,0.0046,0.0013</t>
-  </si>
-  <si>
-    <t>0.9941,0.0015,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9454,0.0671,0.0105,0.0009</t>
-  </si>
-  <si>
-    <t>0.9806,0.0115,0.0037,0.0016</t>
-  </si>
-  <si>
-    <t>0.9847,0.0074,0.0055,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.8078,0.8214,0.0008</t>
-  </si>
-  <si>
-    <t>0.0014,0.7208,0.9374,0.0004</t>
-  </si>
-  <si>
-    <t>0.0428,0.0205,0.9566,0.0007</t>
-  </si>
-  <si>
-    <t>0.0428,0.3383,0.7672,0.0052</t>
-  </si>
-  <si>
-    <t>0.6766,0.1926,0.1425,0.0268</t>
-  </si>
-  <si>
-    <t>0.5790,0.3272,0.1296,0.0099</t>
-  </si>
-  <si>
-    <t>0.6892,0.0214,0.4193,0.0048</t>
-  </si>
-  <si>
-    <t>0.6316,0.1759,0.2287,0.0141</t>
-  </si>
-  <si>
-    <t>0.1354,0.0029,0.0175,0.9133</t>
-  </si>
-  <si>
-    <t>0.0026,0.0012,0.0014,0.9974</t>
-  </si>
-  <si>
-    <t>0.0316,0.0087,0.0084,0.9785</t>
-  </si>
-  <si>
-    <t>0.0877,0.0046,0.0035,0.9719</t>
-  </si>
-  <si>
-    <t>0.0036,0.8510,0.8469,0.0012</t>
-  </si>
-  <si>
-    <t>0.9782,0.0141,0.0031,0.0018</t>
-  </si>
-  <si>
-    <t>0.2132,0.8255,0.0080,0.0079</t>
-  </si>
-  <si>
-    <t>0.9612,0.0142,0.0047,0.0098</t>
-  </si>
-  <si>
-    <t>0.4477,0.6566,0.0171,0.0031</t>
-  </si>
-  <si>
-    <t>0.9448,0.0250,0.0168,0.0091</t>
-  </si>
-  <si>
-    <t>0.8491,0.0099,0.0380,0.0797</t>
-  </si>
-  <si>
-    <t>0.9624,0.0126,0.0094,0.0094</t>
-  </si>
-  <si>
-    <t>0.0073,0.0723,0.9689,0.0113</t>
-  </si>
-  <si>
-    <t>0.9148,0.0072,0.0203,0.0351</t>
-  </si>
-  <si>
-    <t>0.9225,0.0221,0.0231,0.0225</t>
-  </si>
-  <si>
-    <t>0.1477,0.8127,0.0466,0.0592</t>
-  </si>
-  <si>
-    <t>0.7819,0.1959,0.0619,0.0091</t>
-  </si>
-  <si>
-    <t>0.7393,0.3613,0.0130,0.0079</t>
-  </si>
-  <si>
-    <t>0.0636,0.8799,0.0613,0.0345</t>
-  </si>
-  <si>
-    <t>0.7274,0.2382,0.0719,0.0033</t>
-  </si>
-  <si>
-    <t>0.6264,0.4174,0.0398,0.0073</t>
-  </si>
-  <si>
-    <t>0.9891,0.0018,0.0003,0.0038</t>
-  </si>
-  <si>
-    <t>0.9566,0.0429,0.0062,0.0028</t>
-  </si>
-  <si>
-    <t>0.9767,0.0241,0.0034,0.0011</t>
-  </si>
-  <si>
-    <t>0.9918,0.0023,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9863,0.0057,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9521,0.0559,0.0074,0.0022</t>
-  </si>
-  <si>
-    <t>0.9866,0.0038,0.0010,0.0029</t>
-  </si>
-  <si>
-    <t>0.9850,0.0064,0.0016,0.0018</t>
-  </si>
-  <si>
-    <t>0.3849,0.6734,0.0298,0.0042</t>
-  </si>
-  <si>
-    <t>0.5355,0.6150,0.0095,0.0024</t>
-  </si>
-  <si>
-    <t>0.4871,0.5545,0.0238,0.0014</t>
-  </si>
-  <si>
-    <t>0.0790,0.0997,0.8921,0.0030</t>
-  </si>
-  <si>
-    <t>0.9828,0.0217,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.8882,0.1228,0.0300,0.0030</t>
-  </si>
-  <si>
-    <t>0.9730,0.0219,0.0042,0.0015</t>
-  </si>
-  <si>
-    <t>0.9305,0.0762,0.0126,0.0035</t>
-  </si>
-  <si>
-    <t>0.0135,0.0750,0.9681,0.0011</t>
-  </si>
-  <si>
-    <t>0.9363,0.0388,0.0325,0.0019</t>
-  </si>
-  <si>
-    <t>0.0146,0.0077,0.9877,0.0005</t>
-  </si>
-  <si>
-    <t>0.0241,0.0087,0.9733,0.0030</t>
-  </si>
-  <si>
-    <t>0.1158,0.0171,0.9173,0.0032</t>
-  </si>
-  <si>
-    <t>0.0531,0.1712,0.8704,0.0054</t>
-  </si>
-  <si>
-    <t>0.0343,0.0084,0.9772,0.0010</t>
-  </si>
-  <si>
-    <t>0.0099,0.0047,0.9887,0.0009</t>
-  </si>
-  <si>
-    <t>0.0318,0.0061,0.9776,0.0012</t>
-  </si>
-  <si>
-    <t>0.3747,0.2416,0.4298,0.0061</t>
-  </si>
-  <si>
-    <t>0.4491,0.0234,0.7152,0.0010</t>
-  </si>
-  <si>
-    <t>0.1955,0.4846,0.3106,0.0074</t>
-  </si>
-  <si>
-    <t>0.1917,0.2196,0.5601,0.0026</t>
-  </si>
-  <si>
-    <t>0.0655,0.6468,0.4286,0.0116</t>
-  </si>
-  <si>
-    <t>0.2630,0.6096,0.1105,0.0057</t>
-  </si>
-  <si>
-    <t>0.3478,0.3863,0.1844,0.0075</t>
-  </si>
-  <si>
-    <t>0.2972,0.2654,0.4007,0.0024</t>
-  </si>
-  <si>
-    <t>0.0968,0.8987,0.0234,0.0011</t>
-  </si>
-  <si>
-    <t>0.4773,0.5993,0.0163,0.0018</t>
-  </si>
-  <si>
-    <t>0.2937,0.7433,0.0220,0.0071</t>
-  </si>
-  <si>
-    <t>0.9565,0.0654,0.0044,0.0011</t>
-  </si>
-  <si>
-    <t>0.8422,0.2897,0.0055,0.0012</t>
-  </si>
-  <si>
-    <t>0.7426,0.0362,0.2752,0.0093</t>
-  </si>
-  <si>
-    <t>0.8236,0.0116,0.2509,0.0025</t>
-  </si>
-  <si>
-    <t>0.5227,0.0301,0.5364,0.0116</t>
-  </si>
-  <si>
-    <t>0.5646,0.0585,0.5059,0.0074</t>
-  </si>
-  <si>
-    <t>0.7260,0.0134,0.3678,0.0070</t>
-  </si>
-  <si>
-    <t>0.0084,0.0073,0.9866,0.0032</t>
-  </si>
-  <si>
-    <t>0.0460,0.1261,0.8962,0.0188</t>
-  </si>
-  <si>
-    <t>0.0934,0.0723,0.8893,0.0031</t>
-  </si>
-  <si>
-    <t>0.2340,0.0910,0.7099,0.0189</t>
-  </si>
-  <si>
-    <t>0.0836,0.0205,0.9166,0.0087</t>
-  </si>
-  <si>
-    <t>0.9906,0.0039,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.9114,0.1205,0.0157,0.0024</t>
-  </si>
-  <si>
-    <t>0.9575,0.0522,0.0094,0.0015</t>
-  </si>
-  <si>
-    <t>0.9901,0.0080,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9940,0.0030,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9823,0.0212,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9916,0.0033,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9819,0.0105,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.3707,0.0416,0.7134,0.0015</t>
-  </si>
-  <si>
-    <t>0.2878,0.2135,0.5758,0.0072</t>
-  </si>
-  <si>
-    <t>0.7300,0.1403,0.1100,0.0042</t>
-  </si>
-  <si>
-    <t>0.0135,0.0248,0.9730,0.0074</t>
-  </si>
-  <si>
-    <t>0.0057,0.0484,0.9867,0.0011</t>
-  </si>
-  <si>
-    <t>0.1191,0.1612,0.6945,0.0017</t>
-  </si>
-  <si>
-    <t>0.0091,0.0171,0.9866,0.0024</t>
-  </si>
-  <si>
-    <t>0.1598,0.0067,0.9126,0.0015</t>
-  </si>
-  <si>
-    <t>0.0165,0.0341,0.9763,0.0039</t>
-  </si>
-  <si>
-    <t>0.0298,0.0192,0.9605,0.0007</t>
-  </si>
-  <si>
-    <t>0.0475,0.2914,0.7401,0.0014</t>
-  </si>
-  <si>
-    <t>0.5645,0.0374,0.5476,0.0057</t>
-  </si>
-  <si>
-    <t>0.4915,0.0241,0.6023,0.0136</t>
-  </si>
-  <si>
-    <t>0.8160,0.0064,0.1410,0.0156</t>
-  </si>
-  <si>
-    <t>0.9907,0.0083,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9824,0.0150,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.9820,0.0197,0.0022,0.0009</t>
-  </si>
-  <si>
-    <t>0.9859,0.0109,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9960,0.0015,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9781,0.0393,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9875,0.0072,0.0008,0.0015</t>
-  </si>
-  <si>
-    <t>0.9967,0.0026,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0415,0.1044,0.8815,0.0012</t>
-  </si>
-  <si>
-    <t>0.0096,0.0625,0.9741,0.0030</t>
-  </si>
-  <si>
-    <t>0.0677,0.0250,0.9444,0.0025</t>
-  </si>
-  <si>
-    <t>0.1313,0.1068,0.7762,0.0022</t>
-  </si>
-  <si>
-    <t>0.0374,0.0145,0.9603,0.0041</t>
-  </si>
-  <si>
-    <t>0.2730,0.0400,0.7512,0.0143</t>
-  </si>
-  <si>
-    <t>0.2012,0.1039,0.7387,0.0119</t>
-  </si>
-  <si>
-    <t>0.3659,0.0390,0.3272,0.2848</t>
-  </si>
-  <si>
-    <t>0.8690,0.0189,0.0148,0.0972</t>
-  </si>
-  <si>
-    <t>0.0864,0.0178,0.0274,0.9412</t>
-  </si>
-  <si>
-    <t>0.0288,0.0045,0.0047,0.9849</t>
-  </si>
-  <si>
-    <t>0.0118,0.0005,0.0006,0.9961</t>
-  </si>
-  <si>
-    <t>0.0377,0.0022,0.0008,0.9886</t>
-  </si>
-  <si>
-    <t>0.7875,0.0832,0.1092,0.0472</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6512,0.2478,0.1133,0.0598</t>
+  </si>
+  <si>
+    <t>0.0488,0.0077,0.0020,0.9851</t>
+  </si>
+  <si>
+    <t>0.8294,0.0134,0.0394,0.0996</t>
+  </si>
+  <si>
+    <t>0.4071,0.0057,0.0129,0.7304</t>
+  </si>
+  <si>
+    <t>0.9948,0.0019,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9929,0.0068,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9879,0.0113,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0096,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9240,0.1182,0.0090,0.0012</t>
+  </si>
+  <si>
+    <t>0.9933,0.0063,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9825,0.0097,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.9953,0.0018,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.4588,0.2349,0.3347,0.0117</t>
+  </si>
+  <si>
+    <t>0.1596,0.0315,0.8430,0.0057</t>
+  </si>
+  <si>
+    <t>0.1727,0.0075,0.9074,0.0003</t>
+  </si>
+  <si>
+    <t>0.1082,0.0121,0.9208,0.0033</t>
+  </si>
+  <si>
+    <t>0.6552,0.0433,0.3563,0.0275</t>
+  </si>
+  <si>
+    <t>0.0065,0.9854,0.0072,0.0009</t>
+  </si>
+  <si>
+    <t>0.0130,0.9803,0.0109,0.0004</t>
+  </si>
+  <si>
+    <t>0.0973,0.8858,0.0333,0.0021</t>
+  </si>
+  <si>
+    <t>0.0100,0.9779,0.0157,0.0011</t>
+  </si>
+  <si>
+    <t>0.0054,0.9901,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.6406,0.0366,0.4246,0.0075</t>
+  </si>
+  <si>
+    <t>0.4038,0.0394,0.5892,0.0444</t>
+  </si>
+  <si>
+    <t>0.0214,0.0049,0.9835,0.0007</t>
+  </si>
+  <si>
+    <t>0.1626,0.0171,0.8826,0.0041</t>
+  </si>
+  <si>
+    <t>0.0634,0.0142,0.9408,0.0041</t>
+  </si>
+  <si>
+    <t>0.3426,0.0490,0.6136,0.0554</t>
+  </si>
+  <si>
+    <t>0.1362,0.0038,0.9301,0.0020</t>
+  </si>
+  <si>
+    <t>0.3099,0.7213,0.0186,0.0017</t>
+  </si>
+  <si>
+    <t>0.5203,0.1835,0.3394,0.0093</t>
+  </si>
+  <si>
+    <t>0.0772,0.1068,0.8673,0.0228</t>
+  </si>
+  <si>
+    <t>0.0030,0.9912,0.0158,0.0001</t>
+  </si>
+  <si>
+    <t>0.7840,0.1240,0.1328,0.0153</t>
+  </si>
+  <si>
+    <t>0.4723,0.2458,0.2590,0.0032</t>
+  </si>
+  <si>
+    <t>0.7310,0.3345,0.0190,0.0055</t>
+  </si>
+  <si>
+    <t>0.0121,0.9724,0.0493,0.0004</t>
+  </si>
+  <si>
+    <t>0.0248,0.8793,0.2336,0.0099</t>
+  </si>
+  <si>
+    <t>0.1395,0.1198,0.7997,0.0363</t>
+  </si>
+  <si>
+    <t>0.0830,0.0631,0.8913,0.0071</t>
+  </si>
+  <si>
+    <t>0.4675,0.0199,0.5018,0.0315</t>
+  </si>
+  <si>
+    <t>0.0550,0.2301,0.8045,0.0035</t>
+  </si>
+  <si>
+    <t>0.0066,0.9654,0.0988,0.0007</t>
+  </si>
+  <si>
+    <t>0.0860,0.0487,0.8906,0.0169</t>
+  </si>
+  <si>
+    <t>0.0163,0.8003,0.0116,0.7587</t>
+  </si>
+  <si>
+    <t>0.0062,0.9737,0.0354,0.0069</t>
+  </si>
+  <si>
+    <t>0.0095,0.9637,0.1163,0.0016</t>
+  </si>
+  <si>
+    <t>0.0060,0.9750,0.1563,0.0012</t>
+  </si>
+  <si>
+    <t>0.0064,0.0924,0.9739,0.0058</t>
+  </si>
+  <si>
+    <t>0.0019,0.1949,0.9801,0.0014</t>
+  </si>
+  <si>
+    <t>0.0804,0.0164,0.9256,0.0095</t>
+  </si>
+  <si>
+    <t>0.2395,0.0065,0.8339,0.0089</t>
+  </si>
+  <si>
+    <t>0.0145,0.0299,0.9743,0.0016</t>
+  </si>
+  <si>
+    <t>0.0406,0.0170,0.9528,0.0038</t>
+  </si>
+  <si>
+    <t>0.9403,0.0751,0.0093,0.0017</t>
+  </si>
+  <si>
+    <t>0.9767,0.0167,0.0065,0.0009</t>
+  </si>
+  <si>
+    <t>0.9836,0.0084,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.0064,0.6263,0.8723,0.0010</t>
+  </si>
+  <si>
+    <t>0.9070,0.0661,0.0304,0.0127</t>
+  </si>
+  <si>
+    <t>0.9737,0.0287,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.9357,0.0692,0.0137,0.0031</t>
+  </si>
+  <si>
+    <t>0.0066,0.8117,0.8270,0.0020</t>
+  </si>
+  <si>
+    <t>0.0091,0.1198,0.9614,0.0077</t>
+  </si>
+  <si>
+    <t>0.0356,0.0532,0.9203,0.0290</t>
+  </si>
+  <si>
+    <t>0.0024,0.8462,0.9249,0.0005</t>
+  </si>
+  <si>
+    <t>0.0153,0.0059,0.9851,0.0019</t>
+  </si>
+  <si>
+    <t>0.0245,0.9314,0.1111,0.0037</t>
+  </si>
+  <si>
+    <t>0.0067,0.9799,0.0193,0.0014</t>
+  </si>
+  <si>
+    <t>0.3359,0.1019,0.6581,0.0043</t>
+  </si>
+  <si>
+    <t>0.1379,0.3636,0.5639,0.0037</t>
+  </si>
+  <si>
+    <t>0.0051,0.0278,0.9852,0.0024</t>
+  </si>
+  <si>
+    <t>0.0029,0.7852,0.9033,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.7441,0.8910,0.0006</t>
+  </si>
+  <si>
+    <t>0.0065,0.9344,0.4378,0.0025</t>
+  </si>
+  <si>
+    <t>0.0045,0.7206,0.8607,0.0055</t>
+  </si>
+  <si>
+    <t>0.1380,0.0020,0.0561,0.8041</t>
+  </si>
+  <si>
+    <t>0.0092,0.0050,0.0006,0.9961</t>
+  </si>
+  <si>
+    <t>0.0251,0.0016,0.0002,0.9953</t>
+  </si>
+  <si>
+    <t>0.0302,0.0030,0.0018,0.9885</t>
+  </si>
+  <si>
+    <t>0.0891,0.0114,0.0157,0.9523</t>
+  </si>
+  <si>
+    <t>0.0230,0.0027,0.0028,0.9886</t>
+  </si>
+  <si>
+    <t>0.0065,0.9120,0.5649,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.7878,0.9452,0.0001</t>
+  </si>
+  <si>
+    <t>0.0172,0.6559,0.7518,0.0012</t>
+  </si>
+  <si>
+    <t>0.0253,0.5762,0.7880,0.0058</t>
+  </si>
+  <si>
+    <t>0.0023,0.9316,0.7955,0.0004</t>
+  </si>
+  <si>
+    <t>0.0025,0.8569,0.8084,0.0002</t>
+  </si>
+  <si>
+    <t>0.9872,0.0085,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.9798,0.0261,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9822,0.0180,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9865,0.0097,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9718,0.0288,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.9870,0.0094,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9790,0.0232,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9686,0.0323,0.0035,0.0020</t>
+  </si>
+  <si>
+    <t>0.9964,0.0014,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0061,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0015,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9934,0.0058,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9883,0.0093,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9892,0.0064,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0451,0.0170,0.9543,0.0059</t>
+  </si>
+  <si>
+    <t>0.0847,0.0779,0.8635,0.0020</t>
+  </si>
+  <si>
+    <t>0.6637,0.0122,0.3005,0.0237</t>
+  </si>
+  <si>
+    <t>0.1942,0.0072,0.8917,0.0026</t>
+  </si>
+  <si>
+    <t>0.0425,0.9502,0.0108,0.0018</t>
+  </si>
+  <si>
+    <t>0.0131,0.9751,0.0151,0.0009</t>
+  </si>
+  <si>
+    <t>0.1681,0.8812,0.0066,0.0014</t>
+  </si>
+  <si>
+    <t>0.2599,0.7184,0.0423,0.0019</t>
+  </si>
+  <si>
+    <t>0.0245,0.9684,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.0029,0.9938,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.2626,0.8024,0.0050,0.0054</t>
+  </si>
+  <si>
+    <t>0.6970,0.2001,0.1466,0.0150</t>
+  </si>
+  <si>
+    <t>0.3581,0.0114,0.7805,0.0035</t>
+  </si>
+  <si>
+    <t>0.5001,0.3227,0.1332,0.0028</t>
+  </si>
+  <si>
+    <t>0.3615,0.2795,0.2901,0.0029</t>
+  </si>
+  <si>
+    <t>0.5217,0.2603,0.1285,0.1473</t>
+  </si>
+  <si>
+    <t>0.0010,0.9941,0.0301,0.0008</t>
+  </si>
+  <si>
+    <t>0.0111,0.9716,0.0285,0.0029</t>
+  </si>
+  <si>
+    <t>0.0905,0.8391,0.1328,0.0126</t>
+  </si>
+  <si>
+    <t>0.0014,0.9663,0.7521,0.0003</t>
+  </si>
+  <si>
+    <t>0.0219,0.9608,0.0593,0.0005</t>
+  </si>
+  <si>
+    <t>0.4293,0.4877,0.0850,0.0019</t>
+  </si>
+  <si>
+    <t>0.3356,0.6578,0.0348,0.0015</t>
+  </si>
+  <si>
+    <t>0.9768,0.0234,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.9703,0.0285,0.0062,0.0014</t>
+  </si>
+  <si>
+    <t>0.9801,0.0132,0.0046,0.0014</t>
+  </si>
+  <si>
+    <t>0.9842,0.0075,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.9886,0.0092,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9893,0.0057,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9777,0.0080,0.0041,0.0040</t>
+  </si>
+  <si>
+    <t>0.9790,0.0186,0.0070,0.0004</t>
+  </si>
+  <si>
+    <t>0.0132,0.6046,0.8273,0.0021</t>
+  </si>
+  <si>
+    <t>0.0044,0.7929,0.8389,0.0006</t>
+  </si>
+  <si>
+    <t>0.0437,0.0416,0.9503,0.0004</t>
+  </si>
+  <si>
+    <t>0.0395,0.0733,0.9266,0.0007</t>
+  </si>
+  <si>
+    <t>0.6170,0.0319,0.4390,0.0215</t>
+  </si>
+  <si>
+    <t>0.5455,0.1296,0.3788,0.0103</t>
+  </si>
+  <si>
+    <t>0.5572,0.0220,0.5722,0.0045</t>
+  </si>
+  <si>
+    <t>0.7601,0.0856,0.1523,0.0083</t>
+  </si>
+  <si>
+    <t>0.2895,0.0013,0.0090,0.8355</t>
+  </si>
+  <si>
+    <t>0.0030,0.0006,0.0045,0.9950</t>
+  </si>
+  <si>
+    <t>0.1834,0.0096,0.0049,0.9238</t>
+  </si>
+  <si>
+    <t>0.0486,0.0013,0.0054,0.9788</t>
+  </si>
+  <si>
+    <t>0.0021,0.9159,0.7890,0.0009</t>
+  </si>
+  <si>
+    <t>0.9856,0.0127,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0992,0.8798,0.0066,0.0213</t>
+  </si>
+  <si>
+    <t>0.9831,0.0084,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.7246,0.3945,0.0118,0.0017</t>
+  </si>
+  <si>
+    <t>0.9423,0.0185,0.0260,0.0077</t>
+  </si>
+  <si>
+    <t>0.8221,0.0312,0.0830,0.0711</t>
+  </si>
+  <si>
+    <t>0.9814,0.0019,0.0009,0.0077</t>
+  </si>
+  <si>
+    <t>0.0021,0.0439,0.9730,0.0165</t>
+  </si>
+  <si>
+    <t>0.8363,0.0083,0.0299,0.1025</t>
+  </si>
+  <si>
+    <t>0.7247,0.0128,0.0300,0.2626</t>
+  </si>
+  <si>
+    <t>0.1800,0.7475,0.1126,0.0521</t>
+  </si>
+  <si>
+    <t>0.7895,0.1910,0.0548,0.0076</t>
+  </si>
+  <si>
+    <t>0.7657,0.1365,0.1303,0.0055</t>
+  </si>
+  <si>
+    <t>0.6381,0.3948,0.0558,0.0152</t>
+  </si>
+  <si>
+    <t>0.2391,0.7351,0.0365,0.0177</t>
+  </si>
+  <si>
+    <t>0.7900,0.1767,0.0714,0.0093</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9778,0.0230,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9954,0.0020,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0019,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9706,0.0115,0.0023,0.0063</t>
+  </si>
+  <si>
+    <t>0.9624,0.0357,0.0109,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0015,0.0002,0.0036</t>
+  </si>
+  <si>
+    <t>0.9858,0.0036,0.0006,0.0035</t>
+  </si>
+  <si>
+    <t>0.4821,0.5447,0.0416,0.0037</t>
+  </si>
+  <si>
+    <t>0.5819,0.4167,0.0500,0.0039</t>
+  </si>
+  <si>
+    <t>0.0987,0.9075,0.0085,0.0030</t>
+  </si>
+  <si>
+    <t>0.7843,0.1133,0.1606,0.0071</t>
+  </si>
+  <si>
+    <t>0.9671,0.0416,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.9266,0.0516,0.0204,0.0110</t>
+  </si>
+  <si>
+    <t>0.9818,0.0130,0.0036,0.0009</t>
+  </si>
+  <si>
+    <t>0.7983,0.2799,0.0188,0.0042</t>
+  </si>
+  <si>
+    <t>0.0110,0.0340,0.9802,0.0016</t>
+  </si>
+  <si>
+    <t>0.9229,0.0747,0.0224,0.0013</t>
+  </si>
+  <si>
+    <t>0.0309,0.0107,0.9746,0.0009</t>
+  </si>
+  <si>
+    <t>0.0043,0.3284,0.9593,0.0006</t>
+  </si>
+  <si>
+    <t>0.3408,0.0679,0.6659,0.0066</t>
+  </si>
+  <si>
+    <t>0.0508,0.1130,0.9069,0.0067</t>
+  </si>
+  <si>
+    <t>0.0136,0.0186,0.9810,0.0013</t>
+  </si>
+  <si>
+    <t>0.0437,0.0053,0.9643,0.0029</t>
+  </si>
+  <si>
+    <t>0.0060,0.0024,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.3473,0.0344,0.7302,0.0029</t>
+  </si>
+  <si>
+    <t>0.4742,0.0597,0.5693,0.0036</t>
+  </si>
+  <si>
+    <t>0.5988,0.1256,0.3415,0.0072</t>
+  </si>
+  <si>
+    <t>0.3668,0.4995,0.1186,0.0059</t>
+  </si>
+  <si>
+    <t>0.2628,0.5210,0.1204,0.0010</t>
+  </si>
+  <si>
+    <t>0.3251,0.4016,0.1657,0.0037</t>
+  </si>
+  <si>
+    <t>0.5022,0.0558,0.5327,0.0058</t>
+  </si>
+  <si>
+    <t>0.2669,0.0892,0.6670,0.0019</t>
+  </si>
+  <si>
+    <t>0.3929,0.6190,0.0403,0.0027</t>
+  </si>
+  <si>
+    <t>0.8712,0.1945,0.0107,0.0016</t>
+  </si>
+  <si>
+    <t>0.5450,0.5826,0.0158,0.0034</t>
+  </si>
+  <si>
+    <t>0.9704,0.0356,0.0045,0.0009</t>
+  </si>
+  <si>
+    <t>0.9250,0.0992,0.0090,0.0032</t>
+  </si>
+  <si>
+    <t>0.2831,0.6052,0.1933,0.0153</t>
+  </si>
+  <si>
+    <t>0.7685,0.0096,0.3517,0.0015</t>
+  </si>
+  <si>
+    <t>0.7099,0.0175,0.3788,0.0046</t>
+  </si>
+  <si>
+    <t>0.7122,0.0323,0.3301,0.0059</t>
+  </si>
+  <si>
+    <t>0.5840,0.0256,0.4581,0.0244</t>
+  </si>
+  <si>
+    <t>0.0657,0.1990,0.7508,0.0068</t>
+  </si>
+  <si>
+    <t>0.0508,0.2700,0.8363,0.0083</t>
+  </si>
+  <si>
+    <t>0.2222,0.1045,0.7129,0.0612</t>
+  </si>
+  <si>
+    <t>0.2124,0.1918,0.6321,0.0532</t>
+  </si>
+  <si>
+    <t>0.0220,0.1005,0.9379,0.0080</t>
+  </si>
+  <si>
+    <t>0.9877,0.0049,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.9890,0.0081,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9228,0.0718,0.0315,0.0036</t>
+  </si>
+  <si>
+    <t>0.9748,0.0338,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.9901,0.0099,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9872,0.0116,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9909,0.0047,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9646,0.0120,0.0057,0.0088</t>
+  </si>
+  <si>
+    <t>0.1483,0.0347,0.8756,0.0045</t>
+  </si>
+  <si>
+    <t>0.1961,0.2505,0.5604,0.0031</t>
+  </si>
+  <si>
+    <t>0.8785,0.0238,0.0928,0.0182</t>
+  </si>
+  <si>
+    <t>0.0141,0.0599,0.9627,0.0015</t>
+  </si>
+  <si>
+    <t>0.0034,0.0126,0.9929,0.0013</t>
+  </si>
+  <si>
+    <t>0.0380,0.0677,0.9273,0.0010</t>
+  </si>
+  <si>
+    <t>0.0159,0.0182,0.9839,0.0012</t>
+  </si>
+  <si>
+    <t>0.0449,0.0850,0.8737,0.0058</t>
+  </si>
+  <si>
+    <t>0.0065,0.0080,0.9903,0.0017</t>
+  </si>
+  <si>
+    <t>0.0532,0.0199,0.9452,0.0022</t>
+  </si>
+  <si>
+    <t>0.1822,0.0746,0.7535,0.0065</t>
+  </si>
+  <si>
+    <t>0.5111,0.0095,0.5999,0.0105</t>
+  </si>
+  <si>
+    <t>0.7825,0.0045,0.2669,0.0044</t>
+  </si>
+  <si>
+    <t>0.7204,0.0140,0.1381,0.0694</t>
+  </si>
+  <si>
+    <t>0.9788,0.0187,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.9828,0.0203,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9854,0.0076,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.9852,0.0118,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9927,0.0015,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9659,0.0482,0.0037,0.0012</t>
+  </si>
+  <si>
+    <t>0.9957,0.0024,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0033,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.0245,0.1369,0.8928,0.0007</t>
+  </si>
+  <si>
+    <t>0.0071,0.0961,0.9777,0.0007</t>
+  </si>
+  <si>
+    <t>0.0130,0.0209,0.9740,0.0068</t>
+  </si>
+  <si>
+    <t>0.1509,0.1612,0.7033,0.0053</t>
+  </si>
+  <si>
+    <t>0.0560,0.0064,0.9554,0.0050</t>
+  </si>
+  <si>
+    <t>0.7109,0.0178,0.2578,0.0182</t>
+  </si>
+  <si>
+    <t>0.3583,0.0288,0.7516,0.0056</t>
+  </si>
+  <si>
+    <t>0.0348,0.0307,0.8643,0.1064</t>
+  </si>
+  <si>
+    <t>0.8749,0.0118,0.0234,0.0837</t>
+  </si>
+  <si>
+    <t>0.1948,0.0067,0.0150,0.8994</t>
+  </si>
+  <si>
+    <t>0.3086,0.0096,0.0187,0.8058</t>
+  </si>
+  <si>
+    <t>0.0043,0.0004,0.0034,0.9950</t>
+  </si>
+  <si>
+    <t>0.0042,0.0027,0.0008,0.9970</t>
+  </si>
+  <si>
+    <t>0.7569,0.1822,0.1023,0.0247</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2763,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
